--- a/data/input/transactions_202605.xlsx
+++ b/data/input/transactions_202605.xlsx
@@ -13,19 +13,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="41">
   <si>
-    <t>transaction_id</t>
-  </si>
-  <si>
-    <t>customer_id</t>
-  </si>
-  <si>
-    <t>transaction_date</t>
-  </si>
-  <si>
-    <t>amount</t>
-  </si>
-  <si>
-    <t>category</t>
+    <t>取引ID</t>
+  </si>
+  <si>
+    <t>顧客ID</t>
+  </si>
+  <si>
+    <t>取引日</t>
+  </si>
+  <si>
+    <t>金額</t>
+  </si>
+  <si>
+    <t>分類</t>
   </si>
   <si>
     <t>T20260501-001</t>
@@ -37,7 +37,7 @@
     <t>2026-05-01</t>
   </si>
   <si>
-    <t>antibiotic</t>
+    <t>抗生物質</t>
   </si>
   <si>
     <t>T20260501-002</t>
@@ -46,7 +46,7 @@
     <t>C0002</t>
   </si>
   <si>
-    <t>vaccine</t>
+    <t>ワクチン</t>
   </si>
   <si>
     <t>T20260502-001</t>
@@ -73,7 +73,7 @@
     <t>2026-05-05</t>
   </si>
   <si>
-    <t>supplement</t>
+    <t>サプリメント</t>
   </si>
   <si>
     <t>T20260507-001</t>
